--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128615143</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95427</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mäntänoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>821325</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7445278</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128615095</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mäntänoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>821206</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7445201</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95427</v>
+        <v>95433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95433</v>
+        <v>95439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95439</v>
+        <v>95441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95441</v>
+        <v>95442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95442</v>
+        <v>95469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95469</v>
+        <v>95475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95475</v>
+        <v>95482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95482</v>
+        <v>95486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95486</v>
+        <v>95493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95496</v>
+        <v>95501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128585060</v>
       </c>
       <c r="B2" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128615143</v>
       </c>
       <c r="B3" t="n">
-        <v>95501</v>
+        <v>95509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128615095</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128585060</v>
+        <v>128615143</v>
       </c>
       <c r="B2" t="n">
-        <v>83011</v>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haukivuoma, Nb</t>
+          <t>Mäntänoja, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>821067</v>
+        <v>821325</v>
       </c>
       <c r="R2" t="n">
-        <v>7445528</v>
+        <v>7445278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128615143</v>
+        <v>128615095</v>
       </c>
       <c r="B3" t="n">
-        <v>95509</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>821325</v>
+        <v>821206</v>
       </c>
       <c r="R3" t="n">
-        <v>7445278</v>
+        <v>7445201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +857,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128615095</v>
+        <v>128585060</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mäntänoja, Nb</t>
+          <t>Haukivuoma, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>821206</v>
+        <v>821067</v>
       </c>
       <c r="R4" t="n">
-        <v>7445201</v>
+        <v>7445528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,9 +955,19 @@
           <t>2025-07-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,25 +979,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 64979-2021 artfynd.xlsx
+++ b/artfynd/A 64979-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128615143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128615095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>